--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45485</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>46244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45335</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>46043</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>44746</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44462</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>45954</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46169</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44613</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>45518</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45335</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>44937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>44476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45328</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45070</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45226</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>44631</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45964</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45986</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45981</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>46166</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44879</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45205</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45027</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45335</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>45210</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>45370</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>44904</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45335</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44911</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>46030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>45982</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>46055</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>46104</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44792</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>44893</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45978</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45547</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45978</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45973</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44825</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44873</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44488</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44718</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>44462</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44474</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44935</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>44517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45424</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45440</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45919</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45252</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>46145</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45943</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45352</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44466</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>45954</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>46155</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45210</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45993</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>45435</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>45435</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>46013</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45390</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45677</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45530</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46045</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45103</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>46078</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45056</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44621</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45385</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>45603</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>46050</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45145</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>46217</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>46232</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45624</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>46240</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>45820</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>45702</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>44260</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>46268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>44560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44870</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>44811</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>44505</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44656</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>44522</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44510</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>44494</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>44466</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44775</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>44648</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44767</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>44774</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>44753</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44873</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>44652</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>44659</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>44812</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>44732</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>44790</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>44873</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44623</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44705</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44690</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44614</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>44659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44613</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>44491</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44676</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>44812</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44502</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44476</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44530</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>44498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>44505</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>44505</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>44614</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44767</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44662</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44470</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44825</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>44887</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44747</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>44784</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44783</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>44733</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>44733</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44804</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44733</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>44613</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>44614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>44881</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>44812</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44830</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44536</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44813</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>44679</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44853</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>44701</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44704</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44539</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44722</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44652</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>44658</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44522</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44882</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44522</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44862</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>44530</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44537</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44748</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>44719</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>44813</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>44466</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44709</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>44709</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44537</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44729</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>44713</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>44475</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>44505</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44627</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>44463</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>44462</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45365</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>44774</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45268</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45370</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45424</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44515</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45443</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44491</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45301</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44509</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45110</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45210</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44529</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45143</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>45062</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>44579</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44837</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45378</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>44620</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44582</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45352</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>44846</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45201</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44992</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45258</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>44839</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45037</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45419</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45419</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44957</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45044</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45672</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45424</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44968</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44733</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44865</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>45166</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44977</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>44844</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>44964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45146</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>45247</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45244</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45443</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45393</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44529</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45148</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44990</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>44543</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44525</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45159</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45540</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>44825</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>44965</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45162</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45545</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44859</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44879</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45729</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44623</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45335</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45161</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45145</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>44649</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44744</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45315</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45033</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45218</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45603</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45163</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45229</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45166</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44970</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45160</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45161</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45278</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45518</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>44830</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>45132</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>44980</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>44976</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>44867</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45216</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45043</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45162</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45359</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>45329</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45258</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>44510</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45008</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44678</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45183</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44812</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45733</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44579</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45082</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45705</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45379</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>44810</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44620</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45001</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45730</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>44811</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44810</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44830</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>44965</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44774</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44890</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45729</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45729</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>44838</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44839</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>44840</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44817</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44711</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44965</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45365</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>44967</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45986</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>44865</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45819</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>44960</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45826</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>44529</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45524</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>46139</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44853</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44880</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45166</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45888</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45356</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44690</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45096</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44536</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45702</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45559</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>44767</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45187</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44676</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45854</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45819</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45370</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44784</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44553</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>44938</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44881</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45685</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>44825</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>44988</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45706</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45930</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>45058</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45216</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45908</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>44607</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44964</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44995</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>44964</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45170</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45915</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>44634</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32099,7 +32099,7 @@
         <v>45076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>46058</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>45072</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45919</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>44858</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>45350</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45092</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>45729</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45855</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>45098</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>45027</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45761</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>45343</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33068,7 +33068,7 @@
         <v>45855</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>46145</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>44943</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>44943</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45855</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45855</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44650</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44740</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45364</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45410</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45106</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>46145</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>44537</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>44938</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44783</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>44977</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44837</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>46149</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>46149</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45352</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45938</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44998</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>44837</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44837</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>44988</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45944</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45729</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45946</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45721</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45224</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45224</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>46069</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45945</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45945</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45162</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45900</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45349</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>44525</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45384</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>44957</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45820</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45954</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45954</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44578</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45743</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45798</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45112</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>44936</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45603</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>44475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44936</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45721</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45970</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45604</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45329</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>46155</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45414</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>45974</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44616</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45979</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>44645</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44468</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45630</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45351</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45980</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45982</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>44698</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>45603</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>44727</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>44549</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45940</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45029</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45986</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>45061</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44579</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45461</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45993</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45993</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>45993</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45993</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45343</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45149</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45373</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45418</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39622,7 +39622,7 @@
         <v>45603</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>44475</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>46161</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44579</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>46084</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>45398</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45143</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>46072</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>46084</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>45978</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45978</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>46163</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45978</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45993</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45993</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>44916</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45166</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>45999</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45999</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>46001</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>45348</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45327</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46003</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41341,7 +41341,7 @@
         <v>44812</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41414,7 +41414,7 @@
         <v>45279</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>44960</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>46007</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45604</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45630</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>46007</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>46006</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>45721</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>46006</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>46009</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>46168</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>46086</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>46010</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>44783</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44858</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>46010</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46120</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>46010</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>44942</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>46169</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45056</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42967,7 +42967,7 @@
         <v>44911</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45005</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>44530</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>44959</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45162</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>44938</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>45712</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>46027</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43561,7 +43561,7 @@
         <v>45085</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>44790</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>46030</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>46030</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45069</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45474</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45624</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46034</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>46036</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>46036</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>44992</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>46036</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46036</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>44798</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>44728</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>46042</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>45674</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>44799</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>46041</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>46041</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>44881</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45148</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>44525</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>44525</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46098</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>44846</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46049</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45985</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>46176</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45222</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>46049</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46049</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>46049</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>46049</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>44960</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>44960</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>44575</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>46176</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>46176</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>46050</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45546</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45019</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>44582</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45051</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45146</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45174</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>45307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>44938</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45986</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44938</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45986</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45986</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>46071</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>45330</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45075</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>46183</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46071</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>46071</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>44725</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>44606</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>44525</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45110</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>45733</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48245,7 +48245,7 @@
         <v>46131</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>46182</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>44575</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44879</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45096</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>44958</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46184</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>44946</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>46184</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>45166</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>44494</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>46184</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>46184</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45985</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>46185</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>45110</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>45114</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45170</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>44901</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45762</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>46185</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>46185</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>44649</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>44462</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>44944</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>45520</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>46093</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>44497</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>46093</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>44496</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>46100</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>45798</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>46100</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50704,7 +50704,7 @@
         <v>44774</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>45564</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>46100</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50928,7 +50928,7 @@
         <v>45452</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>46195</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51074,7 +51074,7 @@
         <v>45685</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51152,7 +51152,7 @@
         <v>45685</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51230,7 +51230,7 @@
         <v>45986</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45441</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51376,7 +51376,7 @@
         <v>45537</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>46198</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>45667</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>44784</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51678,7 +51678,7 @@
         <v>45098</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45756</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51829,7 +51829,7 @@
         <v>45044</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>45044</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>46245</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>45385</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45062</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45924</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>46114</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45289</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>44536</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>45926</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>44869</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>44546</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>46244</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>44893</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45350</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>44976</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>46245</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>46245</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53251,7 +53251,7 @@
         <v>45602</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>44585</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53397,7 +53397,7 @@
         <v>45098</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53470,7 +53470,7 @@
         <v>45098</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53543,7 +53543,7 @@
         <v>46135</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53616,7 +53616,7 @@
         <v>45559</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>44960</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53762,7 +53762,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53840,7 +53840,7 @@
         <v>44757</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45181</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45964</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45329</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>45218</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45425</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45603</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54371,7 +54371,7 @@
         <v>44711</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54444,7 +54444,7 @@
         <v>46030</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54517,7 +54517,7 @@
         <v>46247</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54590,7 +54590,7 @@
         <v>45350</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54663,7 +54663,7 @@
         <v>44949</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45243</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>44784</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>44462</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>44546</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>44812</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>44477</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>46206</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>44575</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>46247</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55413,7 +55413,7 @@
         <v>45132</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>45132</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>44579</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55642,7 +55642,7 @@
         <v>45224</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45062</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45306</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55861,7 +55861,7 @@
         <v>46253</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55934,7 +55934,7 @@
         <v>44910</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>44869</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56085,7 +56085,7 @@
         <v>45261</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>46211</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56236,7 +56236,7 @@
         <v>44938</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>46253</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56387,7 +56387,7 @@
         <v>45398</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56460,7 +56460,7 @@
         <v>44575</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45628</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>46211</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45062</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56757,7 +56757,7 @@
         <v>45310</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>44652</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56908,7 +56908,7 @@
         <v>44950</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>44977</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>44932</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         <v>44932</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57205,7 +57205,7 @@
         <v>46198</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57278,7 +57278,7 @@
         <v>46198</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45173</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57424,7 +57424,7 @@
         <v>44880</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45040</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>44725</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>44784</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>45029</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>45288</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>44858</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>44968</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45160</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58096,7 +58096,7 @@
         <v>45160</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>45686</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>45727</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58320,7 +58320,7 @@
         <v>45365</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>46222</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45306</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58544,7 +58544,7 @@
         <v>45288</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45547</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>44995</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>44581</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45148</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58909,7 +58909,7 @@
         <v>45712</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>44725</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>44966</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>44540</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59211,7 +59211,7 @@
         <v>45034</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>44830</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>45153</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>46125</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>44489</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>46252</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45775</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>46228</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45190</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59883,7 +59883,7 @@
         <v>44968</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>46234</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45635</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>45524</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>45637</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>46237</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60331,7 +60331,7 @@
         <v>46280</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>46239</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45611</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>46283</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45239</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60706,7 +60706,7 @@
         <v>46240</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>46283</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60852,7 +60852,7 @@
         <v>45672</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60925,7 +60925,7 @@
         <v>45733</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61003,7 +61003,7 @@
         <v>45817</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>45817</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61159,7 +61159,7 @@
         <v>45817</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45819</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>45743</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61388,7 +61388,7 @@
         <v>45831</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>45831</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61539,7 +61539,7 @@
         <v>45834</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45834</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61685,7 +61685,7 @@
         <v>45834</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61758,7 +61758,7 @@
         <v>45834</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>45841</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>45842</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61977,7 +61977,7 @@
         <v>45842</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>45842</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45844</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62196,7 +62196,7 @@
         <v>45842</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62269,7 +62269,7 @@
         <v>45737</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62342,7 +62342,7 @@
         <v>45860</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62420,7 +62420,7 @@
         <v>44944</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>44092</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>44013</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>45223</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62722,7 +62722,7 @@
         <v>44684</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62795,7 +62795,7 @@
         <v>44949</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>44735</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62946,7 +62946,7 @@
         <v>45029</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63019,7 +63019,7 @@
         <v>45714</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45517</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45939</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63253,7 +63253,7 @@
         <v>46090</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63326,7 +63326,7 @@
         <v>46050</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45485</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45335</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45978</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45624</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46093</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44746</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44937</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45954</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>46104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>46169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45518</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45335</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44631</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44879</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>46166</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45328</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>45070</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45226</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45335</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45370</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44904</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46055</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>46104</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45982</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45205</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45335</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45978</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45978</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>45027</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44475</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44911</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>46030</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45973</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>44893</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45547</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>44488</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44718</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>44474</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45424</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45385</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45352</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>46045</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45919</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>46078</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45946</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45954</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45145</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45993</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45820</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>46013</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45440</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46145</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>46155</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45103</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45702</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45435</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45210</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45677</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46050</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46217</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>46232</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46240</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44466</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44517</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45390</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45435</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45056</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44935</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45603</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45624</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44260</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44870</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44811</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>44505</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44656</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44522</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44494</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44510</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44466</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44648</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44775</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44767</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44774</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44753</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44652</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44873</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44659</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44812</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44732</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44790</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44873</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44623</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44705</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44690</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>44614</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44613</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44491</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44676</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>44812</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44502</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44476</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44530</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44505</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44505</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44614</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44767</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44662</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44470</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44825</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44887</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44747</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>44784</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44783</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>44804</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>44733</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>44733</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>44733</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44613</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44881</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>44812</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44536</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44830</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44813</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>44679</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44853</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>44701</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44704</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44722</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44539</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44658</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44652</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44522</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44522</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44882</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44862</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44530</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44537</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44719</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44748</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44813</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44466</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44709</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44709</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44537</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44713</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44729</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44475</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44627</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44784</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44783</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44865</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45008</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45343</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44881</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45378</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45244</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45365</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44825</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44830</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45398</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45441</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44846</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45224</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45224</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45145</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44817</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45288</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44517</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45365</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45258</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44837</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44859</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45359</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44812</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45611</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44837</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44949</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>46027</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45518</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>46030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44477</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44938</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45603</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45603</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45161</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44494</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44936</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45702</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>46034</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>46036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44529</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44536</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>46036</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>46036</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45373</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>46036</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>44992</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46042</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>46041</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45854</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45888</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>44978</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44497</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45329</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>44525</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>46041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45239</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45537</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45352</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45352</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44890</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45685</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46050</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45393</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>46049</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>46049</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>46049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45044</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44525</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44525</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45604</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45005</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45986</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45919</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44938</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>45986</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45110</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>46071</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44620</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45370</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46071</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>46071</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45546</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44896</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45261</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45855</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44537</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45855</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45985</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44944</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45672</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44475</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>44936</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45855</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45855</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46093</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46093</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45944</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45938</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44784</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45218</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45945</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45945</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45072</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45946</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>46100</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46100</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44992</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>46100</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45603</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45900</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45954</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44489</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45547</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44990</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45712</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>44784</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45954</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45820</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45343</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>45733</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45027</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45798</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45924</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>46114</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>44744</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44893</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45110</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45365</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44812</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45258</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45624</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44958</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44960</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>44964</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>44965</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45037</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>44965</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44988</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45970</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45974</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45414</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45817</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45143</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45112</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44998</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44678</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45033</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45817</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45385</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45979</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>44491</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45602</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45062</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45982</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45443</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44733</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45210</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45986</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45819</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45559</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>46135</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>44727</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45727</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45559</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45930</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>44740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45819</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>45826</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>45706</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45993</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45993</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45993</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>45993</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46139</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44977</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>44676</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45999</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45425</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45085</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45999</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>45817</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>46001</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>44582</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34740,7 +34740,7 @@
         <v>44711</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>46003</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45216</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>46006</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>46006</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45545</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44858</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>46007</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>44757</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45224</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>46010</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>46010</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>46009</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46010</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46030</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45729</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45743</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>44575</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45729</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45210</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45761</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45110</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45202</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45672</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45183</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>46058</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45069</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44910</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>45733</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46145</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46145</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>44943</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>44943</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45076</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45831</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45831</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45229</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>46149</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>46149</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>46069</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>46155</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>45940</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45834</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45834</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45351</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45834</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45834</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45978</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45978</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46084</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>45686</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45058</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45733</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45842</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>46084</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45170</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>45842</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>45841</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45162</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45842</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45978</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46072</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44901</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45842</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45844</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45356</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45307</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45107</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45379</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46163</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44960</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45756</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45082</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>45737</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46086</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45040</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>46168</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>46120</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46169</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45350</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45721</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44530</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45132</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45860</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>44496</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44623</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>45098</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>44579</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45335</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45279</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>44944</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45419</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45419</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45159</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45985</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44553</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>44980</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>44995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>44976</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45201</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45029</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>46098</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>44579</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>44525</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45418</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>46176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>44938</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>44575</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45148</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>46176</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>46176</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>44582</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>44546</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45096</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45630</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45306</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45452</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>46131</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45149</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>46184</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>46184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45173</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>44536</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>46183</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>46184</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>46182</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>45132</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45132</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>46185</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>46184</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45148</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45162</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45162</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45243</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44575</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>45181</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>44581</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45146</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45160</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>44995</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>44515</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45721</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45329</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45329</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45798</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>44585</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>45114</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44649</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>46198</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45170</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45986</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45603</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>44606</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>44988</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>44529</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45218</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44839</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>44840</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>44690</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45166</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>46206</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45350</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>45153</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>44652</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45044</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45044</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45730</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>44634</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45061</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>46211</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45187</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>46211</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>46253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45674</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>46198</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45161</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45146</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45166</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>44711</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>46253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>44649</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>44811</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>44810</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>44838</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48845,7 +48845,7 @@
         <v>44839</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>44728</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45166</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45685</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45685</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>44725</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44774</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>44853</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45162</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>46222</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>44645</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>44858</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45222</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>45461</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>44799</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45705</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45712</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>44725</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45289</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>44798</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>44767</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50408,7 +50408,7 @@
         <v>44846</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50481,7 +50481,7 @@
         <v>45348</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45349</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>44607</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>46228</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44810</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>46252</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>46125</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>44974</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45092</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51143,7 +51143,7 @@
         <v>44575</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45271</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>45743</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>44783</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45278</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51508,7 +51508,7 @@
         <v>46237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>46280</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>44620</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45301</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>45628</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>44698</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>44540</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>44967</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>46234</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44830</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>45524</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>44475</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>46239</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>46240</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45327</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>44960</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>44970</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>46283</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>46283</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>44790</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>44880</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>44650</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>44837</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>44879</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>44879</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45001</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         <v>46287</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>44938</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>46245</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>46244</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53768,7 +53768,7 @@
         <v>44916</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45019</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>44812</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>44960</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54070,7 +54070,7 @@
         <v>44938</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45075</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54221,7 +54221,7 @@
         <v>44549</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54294,7 +54294,7 @@
         <v>44977</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>46245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>44869</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>46245</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>46030</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45166</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>46247</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44957</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45062</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45370</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45604</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>46290</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>44946</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45424</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>44959</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>44865</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45216</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>44468</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>44546</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>44968</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>44960</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>44964</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>45166</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>45474</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56169,7 +56169,7 @@
         <v>44543</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>44867</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56315,7 +56315,7 @@
         <v>44616</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>45096</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56461,7 +56461,7 @@
         <v>45098</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56534,7 +56534,7 @@
         <v>45098</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56607,7 +56607,7 @@
         <v>45029</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56680,7 +56680,7 @@
         <v>44525</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>44869</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45034</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>44976</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>44964</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>44510</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>45160</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>45160</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>44837</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>45564</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45729</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>44938</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>44977</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>44509</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>45247</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45061</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57878,7 +57878,7 @@
         <v>44579</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         <v>44579</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45370</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>44579</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45163</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58253,7 +58253,7 @@
         <v>44578</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>45520</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45062</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>44844</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>45143</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>44725</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>45398</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45667</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>45410</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58915,7 +58915,7 @@
         <v>45630</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>45310</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59066,7 +59066,7 @@
         <v>44774</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59139,7 +59139,7 @@
         <v>44968</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59212,7 +59212,7 @@
         <v>45043</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>44880</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45364</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>44881</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>45762</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45148</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59655,7 +59655,7 @@
         <v>44784</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59728,7 +59728,7 @@
         <v>45062</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45721</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59874,7 +59874,7 @@
         <v>44932</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>44932</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>44942</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60093,7 +60093,7 @@
         <v>45174</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>44774</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>44830</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>44965</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45540</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45729</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45729</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45268</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60692,7 +60692,7 @@
         <v>45288</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60765,7 +60765,7 @@
         <v>44529</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45384</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         <v>45106</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45306</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>45603</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>45443</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45424</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>44950</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45350</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45315</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45190</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61593,7 +61593,7 @@
         <v>44968</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>45775</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61744,7 +61744,7 @@
         <v>45635</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61817,7 +61817,7 @@
         <v>45524</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45637</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>44092</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62041,7 +62041,7 @@
         <v>44013</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>44684</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>44735</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>45223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>44949</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45029</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45714</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>45517</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45939</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>46090</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
         <v>46050</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45485</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45335</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45978</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45624</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46093</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44746</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>44937</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45954</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>46104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>46169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45518</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45335</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44476</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44631</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44879</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>46166</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45328</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>45070</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45226</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45335</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45370</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44904</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>46055</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>45210</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>46104</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45982</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44755</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>45205</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45335</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45978</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45978</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>45027</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44475</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>46286</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44911</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>46030</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45973</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>44893</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>45547</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44825</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         <v>44488</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44718</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>44474</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>45424</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45385</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45352</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>46045</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45919</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>46078</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45946</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45954</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45145</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45993</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45820</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         <v>46013</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45440</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>46145</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>46155</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45103</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45702</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45435</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45210</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45677</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46050</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>46217</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>46232</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>46240</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44466</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44517</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45390</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45435</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>45056</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45252</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44935</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45603</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45624</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44260</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46268</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44870</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44811</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>44505</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44656</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44522</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44494</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>44510</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44466</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>44648</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44775</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44767</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44774</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44753</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44652</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44873</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44659</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44812</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44648</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44732</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44790</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44581</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44873</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44623</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44705</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44690</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>44614</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44613</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44491</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44676</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>44812</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44502</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44476</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44530</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44505</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44505</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44614</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44767</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44662</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44470</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44825</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44887</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44747</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>44784</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>44783</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>44804</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>44733</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>44733</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>44733</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44613</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44881</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>44812</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44536</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>44830</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44813</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>44679</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44853</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>44701</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44704</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44722</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44539</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44658</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>44652</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44522</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44522</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>44882</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>44862</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>44530</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44537</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44719</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44748</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44813</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>44525</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44466</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>44709</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44709</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44537</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44713</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44729</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44475</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44627</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44784</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44783</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44865</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45008</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45343</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44881</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45378</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45244</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45365</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44825</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44830</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45398</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45441</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44846</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45224</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45224</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45145</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44817</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45288</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44517</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45365</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45258</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44837</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44859</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45359</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44812</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45611</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44837</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44949</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>46027</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45518</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>46030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44477</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44938</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45603</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45603</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45161</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>44494</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44936</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45702</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>46034</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>46036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44529</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44536</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>46036</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>46036</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45373</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>46036</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>44992</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46042</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>46041</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45854</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45888</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>44978</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44497</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45329</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>44525</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>46041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45239</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45537</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45352</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45352</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>44890</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45685</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46050</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46049</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46049</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45393</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>46049</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>46049</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>46049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45908</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45044</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>44525</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44525</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45604</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45005</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45986</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45986</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45919</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44938</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>45986</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45110</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>46071</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44620</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45370</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46071</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>46071</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45546</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44896</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45261</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45855</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44537</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45855</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45985</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44944</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45672</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44475</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>44936</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45855</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45855</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46093</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46093</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45944</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45938</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44784</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45218</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45945</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45945</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45072</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45946</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>46100</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46100</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44992</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>46100</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45603</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45900</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>45954</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44489</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45547</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44990</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45712</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>44784</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>45954</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45820</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45343</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>45733</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45027</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45798</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45924</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>46114</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>44744</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>44966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44893</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>45110</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45365</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44812</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45258</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45624</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44958</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44960</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>44964</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>44965</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45037</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>44965</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44988</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45970</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45974</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45414</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45817</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45143</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45112</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44998</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>44678</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45033</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45817</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45385</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45979</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>44491</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45602</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45062</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45982</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45443</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44733</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45210</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45986</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45819</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45559</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>46135</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>44727</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45727</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45559</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45930</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>44740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45819</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>45826</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>45706</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45993</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45993</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45993</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>45993</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46139</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>44977</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>44676</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45999</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45425</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45085</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45999</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>45817</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>46001</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>44582</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34740,7 +34740,7 @@
         <v>44711</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>46003</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45216</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
         <v>46006</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>46006</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45545</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44858</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>46007</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>44757</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45224</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>46010</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>46010</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>46009</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46010</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46030</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45729</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45743</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>44575</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45729</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45210</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45761</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45110</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45202</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45672</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45183</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>46058</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45069</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44910</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>45733</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46145</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46145</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>44943</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>44943</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45076</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45831</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45831</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45229</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>46149</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>46149</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>46069</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>46155</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>45940</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45834</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45834</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45351</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45834</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45834</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45978</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45978</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46084</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>45686</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45058</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45733</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45842</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>46084</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45170</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>45842</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>45841</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45162</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45842</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45978</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46072</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44901</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45842</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45844</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45356</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45307</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45107</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45379</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46163</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44960</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45756</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45082</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>45737</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46086</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45040</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>46168</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>46120</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46169</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45350</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45721</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44530</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45132</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45860</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41118,7 +41118,7 @@
         <v>44496</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>44623</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>45098</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>44579</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45335</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45279</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>44944</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45419</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45419</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45159</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45985</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44553</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>44980</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>44995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>44976</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45201</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45029</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>46098</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>44579</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>44525</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45418</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>46176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>44938</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>44575</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45148</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>46176</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>46176</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>44582</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>44546</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45096</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45630</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45306</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45452</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>46131</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45149</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>46184</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>46184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45173</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>44536</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>46183</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>46184</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>46182</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>45132</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45132</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>46185</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44531,7 +44531,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44604,7 +44604,7 @@
         <v>46184</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45148</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45162</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45162</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45243</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44575</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>45181</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>44581</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45146</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45160</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>44995</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>44515</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45721</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45329</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45329</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45798</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>44585</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>45114</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>44649</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>46198</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45170</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45986</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>45603</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>44606</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>44988</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>44529</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45218</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>44839</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>44840</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>44690</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45166</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>46206</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45350</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>45153</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>44652</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45044</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45044</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45730</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>44634</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45061</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>46211</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45187</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>46211</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>46253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45674</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>46198</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45161</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45146</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45166</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>44711</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>46253</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>44649</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>44811</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>44810</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>44838</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48845,7 +48845,7 @@
         <v>44839</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>44728</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45166</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>45685</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45685</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>44725</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44774</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>44853</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>45162</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>46222</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>44645</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>44858</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45222</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>45461</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49892,7 +49892,7 @@
         <v>44799</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45705</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45712</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>44725</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45289</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>44798</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>44767</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50408,7 +50408,7 @@
         <v>44846</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50481,7 +50481,7 @@
         <v>45348</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45349</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>44607</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>46228</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44810</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>46252</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>46125</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>44974</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45092</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51143,7 +51143,7 @@
         <v>44575</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45271</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>45743</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>44783</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45278</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51508,7 +51508,7 @@
         <v>46237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>46280</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>44620</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45301</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51815,7 +51815,7 @@
         <v>45628</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>44698</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>44540</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>44967</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>46234</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44830</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>45524</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>44475</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>46239</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>46240</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45327</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>44960</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>44970</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>46283</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>46283</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>44790</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>44880</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>44650</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>44837</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>44879</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53310,7 +53310,7 @@
         <v>44879</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>45001</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         <v>46287</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>44938</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>46245</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>46244</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53768,7 +53768,7 @@
         <v>44916</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45019</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>44812</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>44960</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54070,7 +54070,7 @@
         <v>44938</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45075</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54221,7 +54221,7 @@
         <v>44549</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54294,7 +54294,7 @@
         <v>44977</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>46245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>44869</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>46245</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>46030</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45166</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>46247</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44957</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45062</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45370</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45604</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>46290</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>44946</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45424</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>44959</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>44865</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45216</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>44468</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>44546</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>44968</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>44960</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>44964</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
         <v>45166</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>45474</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56169,7 +56169,7 @@
         <v>44543</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>44867</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56315,7 +56315,7 @@
         <v>44616</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>45096</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56461,7 +56461,7 @@
         <v>45098</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56534,7 +56534,7 @@
         <v>45098</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56607,7 +56607,7 @@
         <v>45029</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56680,7 +56680,7 @@
         <v>44525</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>44869</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45034</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>44976</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>44964</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>44510</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>45160</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>45160</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>44837</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57352,7 +57352,7 @@
         <v>45564</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45729</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>44938</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>44977</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>44509</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>45247</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45061</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57878,7 +57878,7 @@
         <v>44579</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         <v>44579</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45370</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>44579</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45163</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58253,7 +58253,7 @@
         <v>44578</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>45520</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45062</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>44844</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>45143</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>44725</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>45398</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45667</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>45410</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58915,7 +58915,7 @@
         <v>45630</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>45310</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59066,7 +59066,7 @@
         <v>44774</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59139,7 +59139,7 @@
         <v>44968</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59212,7 +59212,7 @@
         <v>45043</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>44880</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45364</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>44881</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>45762</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45148</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59655,7 +59655,7 @@
         <v>44784</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59728,7 +59728,7 @@
         <v>45062</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45721</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59874,7 +59874,7 @@
         <v>44932</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>44932</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>44942</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60093,7 +60093,7 @@
         <v>45174</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>44774</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>44830</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>44965</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45540</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45729</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60546,7 +60546,7 @@
         <v>45729</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45268</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60692,7 +60692,7 @@
         <v>45288</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60765,7 +60765,7 @@
         <v>44529</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>45384</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         <v>45106</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45306</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>45603</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>45443</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>45424</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>44950</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61364,7 +61364,7 @@
         <v>45350</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61437,7 +61437,7 @@
         <v>45315</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
         <v>45190</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61593,7 +61593,7 @@
         <v>44968</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>45775</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61744,7 +61744,7 @@
         <v>45635</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61817,7 +61817,7 @@
         <v>45524</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45637</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>44092</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62041,7 +62041,7 @@
         <v>44013</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>44684</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>44735</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>45223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>44949</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45029</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45714</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>45517</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45939</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>46090</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62796,7 +62796,7 @@
         <v>46050</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45869</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45485</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45335</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46093</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>46009</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45954</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46104</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45335</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44937</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>44531</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45328</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45964</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45226</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44631</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46166</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44879</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>45205</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45335</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44480</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45370</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>46104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>45982</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44904</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45335</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44475</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>44755</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45978</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45978</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46030</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44792</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45973</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44893</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45547</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44525</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>44488</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44718</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>46013</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>44935</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>46045</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45919</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44517</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45424</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45946</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>46078</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45954</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45820</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45252</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45440</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45352</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>46145</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>46155</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44593</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44960</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45435</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45435</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45390</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>45677</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>46050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45530</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45103</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>46217</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>46232</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>46240</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45056</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44621</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45385</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46295</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45603</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45145</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44260</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>46268</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44560</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44870</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44811</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44505</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44656</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44522</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44494</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44510</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44648</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44775</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44767</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44753</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44652</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44659</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44812</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44774</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44648</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44790</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44873</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44623</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44705</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>44690</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44510</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44614</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>44659</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44530</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44613</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44491</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44676</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44812</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44502</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44476</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44530</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>44498</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44505</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44505</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>44614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44767</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44662</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44887</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44747</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44784</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44783</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44733</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44733</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44804</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44733</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44613</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44614</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44881</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44812</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44536</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44813</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44679</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44701</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44853</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44704</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44578</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44722</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44539</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44658</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44652</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44522</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44882</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44862</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>44531</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>44530</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44537</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>44748</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>44813</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>44525</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44719</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>44709</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44709</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44537</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44729</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44713</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44505</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44627</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45443</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44491</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45365</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44774</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>45268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45301</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44865</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44515</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>44509</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45110</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45210</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45210</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45370</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44579</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45424</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45378</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44837</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44529</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44620</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45143</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45352</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44582</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>44846</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>44992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45258</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44957</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45201</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45672</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45419</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45419</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44733</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45166</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44977</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>44839</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45637</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45037</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45424</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44978</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45148</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44990</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>44968</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>46003</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44844</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46007</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45146</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45393</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>46006</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>46006</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45247</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>46009</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45244</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>44529</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>46010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46010</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46010</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>44525</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44529</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45159</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44543</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45540</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45888</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44825</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46027</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45854</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46030</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45162</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45545</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>46034</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45685</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46036</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46036</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45161</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44859</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>44879</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45729</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46042</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44623</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46041</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46041</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45335</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>44649</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44744</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45315</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45611</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46049</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45915</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>46049</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46049</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45603</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45163</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45145</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45218</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>46050</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45166</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>45160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45919</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45033</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45229</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45855</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44970</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45986</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45855</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45278</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45986</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45518</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45855</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44896</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45855</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>45132</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45161</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>45986</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44830</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>46071</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45216</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>46071</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>46071</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44980</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44976</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44867</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45672</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45162</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45938</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>45043</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45944</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45329</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45359</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45945</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45258</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>44510</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>44678</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45820</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45954</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45954</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44812</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45733</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45985</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45798</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45733</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>45008</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>44579</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45705</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45183</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45082</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45379</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45817</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>44810</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45817</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>46093</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>46093</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45970</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44620</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45730</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>46100</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44811</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44810</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44774</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44817</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44830</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45974</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44965</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45979</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45819</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45982</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45729</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45729</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45743</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44890</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45924</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44838</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44839</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>44840</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>44711</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45993</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45993</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44965</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45365</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45993</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45993</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>45993</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>45993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44967</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45999</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45999</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44865</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>46001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>45831</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45831</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44960</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>46135</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45559</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>44853</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45834</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44880</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45166</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45356</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45096</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>44536</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45834</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45834</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44767</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45964</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45187</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44676</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45370</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>45425</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>44784</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>44553</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>44711</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45841</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>44938</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>46030</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>44881</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>44825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>44988</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45842</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45842</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45842</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>45058</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45844</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45842</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45986</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45216</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>44607</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45819</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44964</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>44995</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44964</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45170</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45826</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>45737</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>44634</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>46139</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45076</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45072</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44858</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>45559</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45819</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45350</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45092</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45729</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45706</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45098</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38607,7 +38607,7 @@
         <v>45930</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45027</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45860</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45761</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45343</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44943</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>44943</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>44650</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44740</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45364</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45410</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45106</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>44537</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>44944</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>44938</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44974</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>44783</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>44977</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>44837</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45352</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>46058</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>44998</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44837</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>44837</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44988</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45202</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45729</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45721</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45224</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45224</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>46145</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45349</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46145</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44525</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45384</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>44957</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46149</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46149</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>44578</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45743</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45112</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>44936</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45603</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>44475</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44936</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45721</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>46155</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45351</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45940</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45604</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45329</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45414</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>46084</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>46072</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>46084</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45978</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>44616</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>46163</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45978</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>44645</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45630</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45721</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>44698</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46168</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45603</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44727</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>46086</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>46120</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>44549</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>46169</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45029</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45061</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45061</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>44579</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45461</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>44517</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>46098</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45343</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45985</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>46176</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45149</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45373</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45418</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>46176</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>46176</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45603</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>44582</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>44475</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>44690</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45702</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>44579</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45398</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>45143</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>46183</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>44916</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46131</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>46182</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45166</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>46184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>46184</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>46184</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>46185</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45348</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>46185</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>46185</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>45327</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>44812</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45279</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44960</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>45604</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46888,7 +46888,7 @@
         <v>45630</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45798</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>46195</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>44783</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>44858</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>45986</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>44942</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>46198</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45056</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>44911</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45005</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>44530</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>44959</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>45162</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>44938</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>45712</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45085</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>44790</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45069</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45474</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45624</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>44992</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>44798</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>44728</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45674</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>46211</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44799</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>44881</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>46211</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45148</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>44525</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>44525</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>44846</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45222</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>44960</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>44960</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>44575</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45546</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45019</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45051</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45146</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>45174</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         <v>45307</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>46222</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>44938</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>44938</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>45330</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>45075</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>44725</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>44606</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>46125</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>44525</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45110</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45733</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>46228</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>44575</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>44879</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>45096</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51280,7 +51280,7 @@
         <v>44958</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>44946</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>45166</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>44494</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46234</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45110</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45114</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>46237</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>45170</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>44901</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46280</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45762</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>44649</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52254,7 +52254,7 @@
         <v>44944</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45520</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>44497</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>46239</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>46283</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>44496</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>44774</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45564</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>46240</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45452</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>46283</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>45685</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>45685</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>46244</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45441</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45537</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         <v>45667</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>44784</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53676,7 +53676,7 @@
         <v>45098</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53749,7 +53749,7 @@
         <v>45756</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45044</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45044</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>46245</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54056,7 +54056,7 @@
         <v>45385</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54129,7 +54129,7 @@
         <v>45062</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54202,7 +54202,7 @@
         <v>45289</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>44536</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54348,7 +54348,7 @@
         <v>45107</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>44869</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>44546</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>46245</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46245</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>46293</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>46247</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>44893</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>46030</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>45350</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>44976</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45945</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45602</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>44585</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>46293</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45098</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>46290</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>46293</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>46293</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>44960</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>45370</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>44757</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45181</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45329</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56228,7 +56228,7 @@
         <v>45218</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56301,7 +56301,7 @@
         <v>46252</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>46253</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45603</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45350</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>44949</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45243</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>44784</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44546</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46253</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46100</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>44812</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>44477</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>44575</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>45132</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>44579</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45224</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>45062</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45306</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57645,7 +57645,7 @@
         <v>44910</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57718,7 +57718,7 @@
         <v>44869</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>45261</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>44938</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>45398</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>44575</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>45628</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45062</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45310</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>44652</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>44950</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>44977</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>44932</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>44932</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45173</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>44880</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>45040</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>44725</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>44784</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59062,7 +59062,7 @@
         <v>45029</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45288</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59208,7 +59208,7 @@
         <v>44858</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>44968</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59359,7 +59359,7 @@
         <v>45160</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>45160</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>45686</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>45727</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>45365</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>45306</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>45288</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59885,7 +59885,7 @@
         <v>45547</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>44995</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60031,7 +60031,7 @@
         <v>44581</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45148</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45712</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60255,7 +60255,7 @@
         <v>44725</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>44966</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60406,7 +60406,7 @@
         <v>44540</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>45034</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60552,7 +60552,7 @@
         <v>44830</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60625,7 +60625,7 @@
         <v>45153</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         <v>44489</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>45775</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45190</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>44968</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>45635</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45524</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>44092</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>44013</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45223</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>44684</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61453,7 +61453,7 @@
         <v>44949</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>44735</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61604,7 +61604,7 @@
         <v>45029</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>45714</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61755,7 +61755,7 @@
         <v>45517</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45939</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>46090</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61984,7 +61984,7 @@
         <v>46050</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45869</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45978</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45485</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45335</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46093</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>46009</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45954</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>46104</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45335</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>44937</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>44531</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45328</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>45964</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45226</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44631</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46166</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44879</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>45205</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45335</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45210</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>46055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44480</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45370</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>46104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>45982</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44904</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45335</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44911</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44475</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>44755</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45978</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45978</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46030</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44792</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45973</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44893</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45547</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44825</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>44525</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>44488</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>44718</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>46013</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>44935</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45677</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>46045</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45919</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         <v>44517</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45424</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45946</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>46078</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45954</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45820</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45993</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45252</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45440</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45352</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>46145</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>46155</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44593</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44960</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>45435</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45435</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45390</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>45677</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>46050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>45530</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>45103</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>46217</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>46232</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>46240</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45056</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44621</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45385</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46295</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45603</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45145</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44260</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>46268</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44560</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44870</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44811</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44505</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44656</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44522</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44494</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44510</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44648</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44775</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44767</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44733</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44753</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44873</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44652</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44659</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44812</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44774</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44648</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44732</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44790</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44873</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>44623</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44705</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>44690</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44510</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44614</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>44659</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44530</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44613</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44491</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44676</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44812</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>44502</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44476</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>44530</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>44498</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44505</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44505</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>44614</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44767</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44662</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44825</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44887</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44747</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44784</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44783</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44733</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>44733</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>44804</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44733</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44613</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44614</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44881</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44812</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44536</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44813</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44679</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44701</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44853</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44704</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>44578</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>44722</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44539</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44658</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44652</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44522</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44522</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44882</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44862</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>44531</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>44530</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44537</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>44748</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>44813</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>44525</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44719</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>44709</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44709</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44537</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44729</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44713</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44475</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44505</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44627</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45443</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44491</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45365</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44774</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>45268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45301</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44865</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44515</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>44509</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45110</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>45210</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45210</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45370</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44579</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45424</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45378</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44837</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44529</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44620</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45143</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45352</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44582</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>44846</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>44992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45258</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44957</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45201</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45672</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45419</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45419</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>44733</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45166</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44977</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>44839</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45637</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45037</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45424</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44978</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45148</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44990</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>44968</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>46003</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44844</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46007</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45146</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45393</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>46006</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>46006</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45247</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>46009</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>45244</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>44529</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>46010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46010</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>46010</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>44525</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44529</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45159</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44543</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45540</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45888</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44825</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46027</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45854</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46030</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45162</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45545</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>46034</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45685</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46036</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46036</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45161</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44859</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>44879</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45729</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46042</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44623</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46041</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46041</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45335</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>44649</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>44744</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45315</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45611</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>46049</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45915</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>46049</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46049</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45603</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45163</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45145</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45218</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>46050</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45166</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>45160</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45919</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45033</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45229</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45855</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44970</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45986</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45855</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45278</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45986</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45518</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45855</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44896</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45855</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>45132</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45161</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>45986</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>44830</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>46071</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45216</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>46071</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>46071</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44980</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44976</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44867</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45672</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45162</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45938</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>45043</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45944</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45329</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45359</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45945</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45258</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>44510</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>44678</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45820</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45954</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45954</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>44812</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45733</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45985</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45798</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45733</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>45008</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>44579</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45705</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45183</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45082</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45379</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45817</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>44810</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45817</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>46093</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>46093</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45970</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44620</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45730</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>46100</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44811</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44810</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>44774</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44817</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>44830</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45974</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44965</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45979</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45819</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45982</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45729</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45729</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45743</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44890</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45924</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>44838</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44839</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>44840</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>44711</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45993</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45993</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44965</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45365</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45993</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45993</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>45993</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>45993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>44967</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45999</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45999</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44865</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>46001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>45831</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45831</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>44960</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>46135</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45559</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34678,7 +34678,7 @@
         <v>44853</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34751,7 +34751,7 @@
         <v>45834</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44880</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45166</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>45356</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45096</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>44536</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45834</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45834</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44767</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45964</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45187</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44676</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45370</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>45425</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>44784</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>44553</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>44711</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45841</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>44938</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>46030</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>44881</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>44825</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>44988</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>45842</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45842</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36679,7 +36679,7 @@
         <v>45842</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>45058</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45844</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45842</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45986</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45216</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>44607</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45819</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>44964</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>44995</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44964</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>45170</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>45826</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>45737</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>44634</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37784,7 +37784,7 @@
         <v>46139</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45076</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45072</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44858</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>45559</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45819</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45350</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45092</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45729</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45706</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45098</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38607,7 +38607,7 @@
         <v>45930</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45027</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45860</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45761</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45343</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44943</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>44943</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>44650</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44740</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45364</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45410</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45106</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>44537</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>44944</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>44938</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44974</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>44783</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>44977</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>44837</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45352</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>46058</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>44998</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44837</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>44837</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44988</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45202</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45729</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45721</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45224</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45224</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>46145</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45349</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46145</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44525</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45384</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>44957</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>46149</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46149</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>44578</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45743</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45112</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>44936</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45603</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>44475</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>44936</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45721</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>46155</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>45351</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45940</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45604</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45329</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45414</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>46084</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>46072</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>46084</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45978</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>44616</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>46163</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45978</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>44645</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45630</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45721</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>44698</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>46168</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45603</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44727</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>46086</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>46120</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>44549</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>46169</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45029</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45061</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45061</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>44579</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45461</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>44517</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>46098</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45343</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45985</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>46176</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45149</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45373</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45418</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>46176</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>46176</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45603</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>44582</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>44475</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>44690</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45702</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>44579</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45398</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>45143</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>46183</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>44916</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46131</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>46182</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45166</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>46184</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>46184</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>46184</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>46185</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45348</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>46185</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>46185</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>45327</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>44812</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45279</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>44960</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>45604</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46888,7 +46888,7 @@
         <v>45630</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46961,7 +46961,7 @@
         <v>45798</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>46195</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>44783</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>44858</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>45986</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>44942</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>46198</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45056</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>44911</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45005</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>44530</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>44959</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>45162</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>44938</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47993,7 +47993,7 @@
         <v>45712</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>45085</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>44790</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45069</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45474</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45624</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>44992</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>44798</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>44728</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45674</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>46211</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>44799</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>44881</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>46211</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>45148</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>44525</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>44525</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>44846</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45222</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>44960</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>44960</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>44575</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45546</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45019</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45051</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45146</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>45174</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         <v>45307</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>46222</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>44938</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>44938</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>45330</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>45075</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50525,7 +50525,7 @@
         <v>44725</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>44606</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>46125</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>44525</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50827,7 +50827,7 @@
         <v>45110</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45733</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>46228</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>44575</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         <v>44879</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>45096</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51280,7 +51280,7 @@
         <v>44958</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>44946</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>45166</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>44494</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>46234</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45110</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45114</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51801,7 +51801,7 @@
         <v>46237</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>45170</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>44901</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46280</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45762</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>44649</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52254,7 +52254,7 @@
         <v>44944</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45520</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>44497</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>46239</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>46283</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>44496</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>44774</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>45564</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>46240</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>45452</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>46283</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>45685</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>45685</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53223,7 +53223,7 @@
         <v>46244</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45441</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45537</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         <v>45667</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53525,7 +53525,7 @@
         <v>44784</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>46287</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53676,7 +53676,7 @@
         <v>45098</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53749,7 +53749,7 @@
         <v>45756</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45044</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>45044</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53978,7 +53978,7 @@
         <v>46245</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54056,7 +54056,7 @@
         <v>45385</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54129,7 +54129,7 @@
         <v>45062</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54202,7 +54202,7 @@
         <v>45289</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54275,7 +54275,7 @@
         <v>44536</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54348,7 +54348,7 @@
         <v>45107</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54421,7 +54421,7 @@
         <v>44869</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>44546</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>46245</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46245</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>46293</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>46247</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>44893</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>46030</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>45350</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>44976</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45945</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45602</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>44585</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>46293</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45098</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>46290</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>46293</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>46293</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>44960</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>45370</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>44757</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45181</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45329</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56228,7 +56228,7 @@
         <v>45218</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56301,7 +56301,7 @@
         <v>46252</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>46253</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45603</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         <v>45350</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>44949</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56676,7 +56676,7 @@
         <v>45243</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>44784</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44546</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46253</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46100</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>44812</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>44477</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>44575</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>45132</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>44579</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45224</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>45062</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45306</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57645,7 +57645,7 @@
         <v>44910</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57718,7 +57718,7 @@
         <v>44869</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57796,7 +57796,7 @@
         <v>45261</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>44938</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>45398</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>44575</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>45628</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45062</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>45310</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>44652</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>44950</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>44977</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>44932</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58619,7 +58619,7 @@
         <v>44932</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45173</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58765,7 +58765,7 @@
         <v>44880</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>45040</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>44725</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>44784</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59062,7 +59062,7 @@
         <v>45029</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45288</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59208,7 +59208,7 @@
         <v>44858</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>44968</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59359,7 +59359,7 @@
         <v>45160</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>45160</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>45686</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59588,7 +59588,7 @@
         <v>45727</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>45365</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>45306</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>45288</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59885,7 +59885,7 @@
         <v>45547</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>44995</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60031,7 +60031,7 @@
         <v>44581</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45148</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45712</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60255,7 +60255,7 @@
         <v>44725</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>44966</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60406,7 +60406,7 @@
         <v>44540</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>45034</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60552,7 +60552,7 @@
         <v>44830</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60625,7 +60625,7 @@
         <v>45153</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         <v>44489</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>45775</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45190</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>44968</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>45635</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45524</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>44092</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61229,7 +61229,7 @@
         <v>44013</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45223</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>44684</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61453,7 +61453,7 @@
         <v>44949</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>44735</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61604,7 +61604,7 @@
         <v>45029</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>45714</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61755,7 +61755,7 @@
         <v>45517</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45939</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>46090</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61984,7 +61984,7 @@
         <v>46050</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>44543</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>45244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45335</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45485</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45624</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45869</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>46043</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44746</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45518</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45335</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45954</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>46075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45328</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44631</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44879</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45070</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45226</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>45981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46166</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44893</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45335</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44480</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44904</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45335</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>45210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44755</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45982</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45027</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>46104</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44911</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>46055</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>46050</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>46030</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45978</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45978</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>45973</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44873</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44525</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44488</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44718</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45424</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45435</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45252</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45103</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45385</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44935</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45603</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45352</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45919</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45624</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45435</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45210</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45677</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44621</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45820</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45145</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45702</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45530</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45993</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>46013</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44593</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44517</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45390</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45677</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>46045</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45440</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>46145</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>46078</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46155</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>46217</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>46232</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>46240</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>46295</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>44260</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44560</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>44870</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44811</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44505</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44656</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44522</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>44494</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44510</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44648</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44775</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44767</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44774</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44733</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44753</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44873</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44652</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>44659</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>44812</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44648</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>44732</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44581</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44790</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44873</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>44623</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44705</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>44690</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44510</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>44614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44659</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44613</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44530</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44491</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44676</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44812</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>44502</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44530</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44498</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44505</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44505</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44539</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44614</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44652</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44658</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>44522</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44767</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44522</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>44812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44882</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44719</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>44662</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>44748</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44813</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44862</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44830</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44531</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44536</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44813</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44825</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44679</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44887</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44784</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44853</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44701</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44704</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44783</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44733</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44733</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44709</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44709</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44804</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44530</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44733</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44613</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44722</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>44729</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>44713</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44627</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44881</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45378</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45061</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44858</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44505</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>44830</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45365</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>44825</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45229</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44579</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44579</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45370</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45441</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>44579</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>44578</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45520</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45244</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45398</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>44784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44783</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45062</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>44844</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45143</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44725</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45398</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45667</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>44865</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45410</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45686</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>45058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>44846</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45288</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45733</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45630</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45330</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45310</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45224</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45224</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45145</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44817</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45343</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45170</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>44774</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45162</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>44517</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45365</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45356</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45307</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45107</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>44837</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44859</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44968</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45379</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44880</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>44960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45258</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45756</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45364</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45082</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44529</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44881</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45359</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45040</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45762</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45148</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44784</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44812</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45350</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44690</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45062</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44932</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44932</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>44530</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44942</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45174</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>44837</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44949</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45132</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44496</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44774</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44830</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45702</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>44623</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45518</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45098</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44965</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>44579</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45540</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45335</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45279</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45419</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45419</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45159</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45729</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45729</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45268</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45288</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>44553</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45603</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>44980</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44995</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45603</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44976</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>44529</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45161</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45854</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44494</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45384</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44936</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44529</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44536</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45106</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45685</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45306</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45603</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45373</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45201</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45029</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45443</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45424</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>44992</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>44950</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>44579</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>44525</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45350</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45418</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44938</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>44575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45148</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44978</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44497</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45329</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>44525</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45537</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45315</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45352</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45352</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44890</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44546</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45096</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45630</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45190</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45306</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44968</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>45393</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45452</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45149</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45915</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45173</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44536</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45044</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44525</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44525</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45056</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45132</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45148</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45162</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45243</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44575</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45181</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45604</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45919</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>44581</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45635</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45146</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45005</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45160</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44995</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>44515</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45524</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>44938</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45721</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45637</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45110</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>44620</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45329</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45329</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45370</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45546</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44896</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45261</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>44585</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45114</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45611</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45855</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45855</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>44649</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44537</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44957</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44911</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45170</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45051</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44936</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>45603</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45239</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>44606</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44988</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45218</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44839</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>44840</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45855</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45855</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45166</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>44784</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45350</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45218</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45153</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45072</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>44652</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>45044</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45044</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>44992</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>45730</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>44634</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45061</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45187</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45603</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45944</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>44489</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45946</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45547</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44990</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45712</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44784</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45674</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45817</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45343</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>45027</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45817</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45817</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>44744</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>44966</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>45161</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44893</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45146</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45819</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45110</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45365</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45743</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>44812</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45258</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45166</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45624</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>44711</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44958</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44960</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>44649</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44811</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>44810</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>44838</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>44965</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44839</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45037</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>44965</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>44988</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45831</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45831</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45900</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45954</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45954</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45414</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>45820</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45798</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>44728</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45143</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45166</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45685</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45685</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45834</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45834</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45112</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45834</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45834</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>44725</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44998</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>44774</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>44678</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>44853</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45033</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>45385</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>44491</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45602</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45062</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44645</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45443</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>45842</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>44858</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>44733</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45842</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45841</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45210</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45842</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45842</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45222</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45461</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>44799</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45844</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45970</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>44727</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45705</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45712</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45974</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>44725</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45727</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44740</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45737</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>44798</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45860</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44977</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>44676</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44767</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45085</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>45348</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45349</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44607</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>44582</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>44810</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45216</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>45545</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         <v>44858</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44757</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45224</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>44974</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>45980</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45092</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45979</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>44575</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45729</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>44575</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>45982</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45729</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45210</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>45271</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>45743</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>45761</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45110</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>45202</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44783</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45672</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>45278</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>46100</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44620</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45301</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45628</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>44698</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>44540</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>44967</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45183</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45069</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>44830</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>44910</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45524</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45733</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>44825</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>45327</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>44943</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44943</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45924</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>46114</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44960</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>44970</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45993</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45993</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45993</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45993</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45993</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44790</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45993</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>44880</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>44650</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>44837</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>44879</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>44879</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45001</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45999</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45999</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>46001</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>44938</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44916</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>45019</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>44812</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>44960</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>44938</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>46006</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45075</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>46006</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44549</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>44977</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44869</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46007</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45166</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44957</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>45062</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45986</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45819</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>45370</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45559</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>45604</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>46135</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>45964</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>44946</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>46010</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>46010</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50108,7 +50108,7 @@
         <v>45559</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>46009</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>46010</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>45930</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>45819</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45826</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45706</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>46139</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45424</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>44959</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>46027</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>44865</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>45216</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45425</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>46030</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>44546</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>44968</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51369,7 +51369,7 @@
         <v>44711</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>44960</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>44964</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45166</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45474</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>44543</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>46034</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>44867</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51963,7 +51963,7 @@
         <v>46036</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52036,7 +52036,7 @@
         <v>44616</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>46036</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>45096</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52255,7 +52255,7 @@
         <v>46036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45098</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45098</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45029</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44525</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>44869</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>46036</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>46042</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>46041</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52927,7 +52927,7 @@
         <v>46030</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53000,7 +53000,7 @@
         <v>46041</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45034</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>44976</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>44964</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>44510</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>45160</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>45160</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>44837</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45564</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>46050</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>45729</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>46049</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>44938</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>44977</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>46049</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>44509</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54188,7 +54188,7 @@
         <v>45247</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>46049</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>46049</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         <v>46058</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54485,7 +54485,7 @@
         <v>45986</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>46145</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>46145</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45986</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45986</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>46149</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>46149</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54996,7 +54996,7 @@
         <v>46071</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55069,7 +55069,7 @@
         <v>46071</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>46071</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>45985</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55288,7 +55288,7 @@
         <v>46155</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55361,7 +55361,7 @@
         <v>45940</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45978</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55590,7 +55590,7 @@
         <v>45978</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>46093</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>46093</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>46084</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>46084</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>46072</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46163</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56106,7 +56106,7 @@
         <v>46086</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>46168</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>46120</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>46169</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>45721</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45985</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>46098</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>46176</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56700,7 +56700,7 @@
         <v>46176</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>46176</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>44582</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56919,7 +56919,7 @@
         <v>46184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
         <v>46184</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>46183</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57138,7 +57138,7 @@
         <v>46184</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>46182</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>46185</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>46185</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>46185</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57508,7 +57508,7 @@
         <v>46184</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57586,7 +57586,7 @@
         <v>46195</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45798</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>46198</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>46206</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>46211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>46211</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>46222</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>46228</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>46125</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46237</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>46280</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46234</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>46239</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>46240</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>46283</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>46283</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46287</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58852,7 +58852,7 @@
         <v>46245</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>46244</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46245</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>46245</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>46030</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>46247</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>46290</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
         <v>46247</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59471,7 +59471,7 @@
         <v>46293</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59544,7 +59544,7 @@
         <v>46293</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45945</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59695,7 +59695,7 @@
         <v>46293</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>46293</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>46252</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46253</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>46253</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>46100</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45986</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60226,7 +60226,7 @@
         <v>46003</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>44092</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>44013</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60450,7 +60450,7 @@
         <v>44684</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>44735</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>45223</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60679,7 +60679,7 @@
         <v>44949</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60752,7 +60752,7 @@
         <v>45029</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60825,7 +60825,7 @@
         <v>45714</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60903,7 +60903,7 @@
         <v>45517</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45939</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>46090</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61132,7 +61132,7 @@
         <v>46050</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>44543</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>45244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45335</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>45485</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45624</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45869</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>46043</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44726</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44746</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45518</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45335</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45954</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>46075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45328</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44631</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44879</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>44817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45070</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45226</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>45981</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46166</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44893</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45335</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44480</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44904</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45335</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>45210</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>44792</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44755</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>45982</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>45027</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>46104</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44911</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>46055</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>46050</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>46286</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>46030</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45978</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45978</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>45973</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44825</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>44873</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44525</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>44488</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44718</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45424</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45435</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>45252</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45103</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45385</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44935</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45603</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45352</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>45919</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45624</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45435</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>45210</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45677</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44621</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>45946</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45820</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45954</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45145</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45702</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45530</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45993</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>46013</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44593</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44517</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45390</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45677</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>46045</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45440</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>46145</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>46078</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>46155</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>46217</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>46232</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>46240</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>46295</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>44260</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>46268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44560</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>44870</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44811</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>44505</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44656</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44522</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>44494</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>44510</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44648</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44775</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>44767</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44774</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44733</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44753</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44873</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44652</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>44659</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>44812</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44648</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>44732</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44581</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44790</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44873</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>44623</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44705</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>44690</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44510</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>44614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>44659</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44613</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>44530</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44491</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44676</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44812</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>44502</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>44530</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44498</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44505</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44505</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44539</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44537</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44614</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>44881</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44652</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44658</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>44522</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44767</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44522</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>44812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44882</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44719</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>44662</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>44748</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44813</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44862</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44830</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44531</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44536</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44813</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44825</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44679</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44887</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44784</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44853</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44701</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44704</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44783</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44733</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44733</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44709</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44709</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>44804</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44530</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44733</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44613</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>44722</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>44729</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>44713</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44627</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44881</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45378</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45061</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44858</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44505</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>44830</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>45365</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>44825</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>45229</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>44579</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>44579</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45370</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45441</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>44579</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>44578</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45520</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45244</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45398</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>44784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44783</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45062</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>44844</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>45143</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44725</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45398</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45667</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>44865</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>45410</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45686</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20945,7 +20945,7 @@
         <v>45058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>44846</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45288</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45733</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45630</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45330</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45310</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45224</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45224</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45145</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44817</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45343</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45170</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>44774</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45162</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>44517</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45365</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>44901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45356</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>45307</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45107</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>44837</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44859</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44968</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45379</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45043</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44880</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>44960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45258</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45756</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45364</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45082</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44529</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44881</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45359</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45040</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45762</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45148</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44784</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44812</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45350</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44690</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45062</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44932</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>44932</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>44530</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44942</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45174</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>44837</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44949</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45132</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44496</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44774</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44830</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45702</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>44623</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45518</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45098</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44965</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>44579</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45540</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45335</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45279</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45419</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45419</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45159</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45729</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45729</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45268</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44938</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45288</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>44553</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45603</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>44980</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>44995</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45603</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44976</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>44529</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45161</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45854</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>44494</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45384</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>44936</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>44529</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44536</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45106</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45685</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>45306</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45603</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         <v>45373</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45201</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45029</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45443</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45424</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>44992</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>44950</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>44579</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>44525</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45350</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45418</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>44938</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>44575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45148</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44978</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44497</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45329</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>44525</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45537</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45315</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45352</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45352</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>44890</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44546</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45096</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45630</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45190</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45306</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44968</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>45393</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45452</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45149</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45915</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>45173</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>44536</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45044</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44525</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44525</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45056</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45132</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45148</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45162</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45243</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44575</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45181</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45604</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>45919</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>44581</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45635</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45146</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45005</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45160</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44995</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>44515</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45524</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>44938</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45721</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45637</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45110</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>44620</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45329</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45329</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45370</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45546</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44896</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>45261</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>44585</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45114</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45611</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45855</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>45855</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>44649</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44537</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44957</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44911</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45170</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45051</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44936</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>45603</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45239</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>44606</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44988</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45218</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44839</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>44840</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45855</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45855</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
         <v>45166</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>44784</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45350</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45218</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45153</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45072</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>44652</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>45044</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45044</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>44992</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>45730</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
         <v>44634</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45061</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45187</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45603</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45944</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45938</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45733</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>44489</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45946</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45547</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44990</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45712</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44784</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>45674</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45817</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45343</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>45027</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45817</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45817</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>44744</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>44966</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>45161</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44893</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45146</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45819</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45110</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45365</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45743</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>44812</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45258</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45166</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45624</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>44711</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44958</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44960</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>44649</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44964</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44811</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>44810</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>44838</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>44965</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44839</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45037</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>44965</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>44988</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45831</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45831</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45900</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38928,7 +38928,7 @@
         <v>45954</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45954</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>45414</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>45820</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45798</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>44728</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45143</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45166</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45685</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45685</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45834</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45834</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45112</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45834</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45834</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>44725</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44998</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>44774</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>44678</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>44853</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45033</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40501,7 +40501,7 @@
         <v>45385</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40574,7 +40574,7 @@
         <v>44491</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45602</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45062</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44645</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45443</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>45842</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>44858</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>44733</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45842</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45841</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>45210</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45842</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45842</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45222</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45461</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>44799</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45844</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45970</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>44727</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45705</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>45712</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45974</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>44725</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45727</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>44740</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45737</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>44798</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45860</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44977</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>44676</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44767</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>44846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45085</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>44944</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>45348</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>45349</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>44607</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>44582</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43534,7 +43534,7 @@
         <v>44810</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45216</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>45545</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43753,7 +43753,7 @@
         <v>44858</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44757</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45224</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>44974</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>45980</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45092</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45979</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>44575</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45729</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>44575</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>45982</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45729</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45210</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>45271</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>45743</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44868,7 +44868,7 @@
         <v>45761</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45110</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>45202</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44783</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45160,7 +45160,7 @@
         <v>45672</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45233,7 +45233,7 @@
         <v>45278</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>46100</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>44620</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45301</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45628</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>44698</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>44540</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>44967</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45183</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45069</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>44830</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>44910</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45524</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45733</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>44825</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>45327</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>44943</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44943</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45924</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>46114</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44960</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>44970</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45993</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45993</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45993</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45993</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45993</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44790</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45993</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>44880</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>44650</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>44837</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>44879</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>44879</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45001</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>45999</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45999</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>46001</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>44938</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44916</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>45019</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>44812</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>44960</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>44938</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>46006</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>45075</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>46006</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>44549</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>44977</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44869</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46007</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>45166</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44957</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>45062</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45986</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45819</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>45370</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>45559</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>45604</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>46135</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>45964</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49889,7 +49889,7 @@
         <v>44946</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>46010</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>46010</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50108,7 +50108,7 @@
         <v>45559</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>46009</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>46010</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50327,7 +50327,7 @@
         <v>45930</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50400,7 +50400,7 @@
         <v>45819</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45826</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>45706</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>46139</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45424</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>44959</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>46027</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>44865</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50994,7 +50994,7 @@
         <v>45216</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45425</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>46030</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51218,7 +51218,7 @@
         <v>44546</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>44968</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51369,7 +51369,7 @@
         <v>44711</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51442,7 +51442,7 @@
         <v>44960</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>44964</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45166</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45474</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         <v>44543</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51812,7 +51812,7 @@
         <v>46034</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>44867</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51963,7 +51963,7 @@
         <v>46036</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52036,7 +52036,7 @@
         <v>44616</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>46036</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>45096</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52255,7 +52255,7 @@
         <v>46036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45098</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45098</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45029</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44525</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>44869</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>46036</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>46042</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>46041</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52927,7 +52927,7 @@
         <v>46030</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53000,7 +53000,7 @@
         <v>46041</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>45034</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>44976</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>44964</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>44510</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>45160</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>45160</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>44837</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45564</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53672,7 +53672,7 @@
         <v>46050</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>45729</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>46049</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>44938</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>44977</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>46049</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>44509</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54188,7 +54188,7 @@
         <v>45247</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>46049</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54339,7 +54339,7 @@
         <v>46049</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         <v>46058</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54485,7 +54485,7 @@
         <v>45986</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>46145</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>46145</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>45986</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54777,7 +54777,7 @@
         <v>45986</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>46149</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54923,7 +54923,7 @@
         <v>46149</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54996,7 +54996,7 @@
         <v>46071</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55069,7 +55069,7 @@
         <v>46071</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>46071</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>45985</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55288,7 +55288,7 @@
         <v>46155</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55361,7 +55361,7 @@
         <v>45940</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45351</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45978</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55590,7 +55590,7 @@
         <v>45978</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>46093</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>46093</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>46084</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>46084</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>46072</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>46163</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56106,7 +56106,7 @@
         <v>46086</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>46168</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>46120</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>46169</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>45721</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45985</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>46098</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>46176</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56700,7 +56700,7 @@
         <v>46176</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>46176</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>44582</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56919,7 +56919,7 @@
         <v>46184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
         <v>46184</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>46183</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57138,7 +57138,7 @@
         <v>46184</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>46182</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>46185</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>46185</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>46185</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57508,7 +57508,7 @@
         <v>46184</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57586,7 +57586,7 @@
         <v>46195</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45798</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>46198</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>46206</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>46211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>46211</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>46222</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>46228</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>46125</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46237</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>46280</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46234</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>46239</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>46240</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>46283</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>46283</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46287</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58852,7 +58852,7 @@
         <v>46245</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>46244</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46245</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>46245</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>46030</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>46247</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>46290</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
         <v>46247</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59471,7 +59471,7 @@
         <v>46293</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59544,7 +59544,7 @@
         <v>46293</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45945</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59695,7 +59695,7 @@
         <v>46293</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>46293</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>46252</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46253</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>46253</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>46100</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60153,7 +60153,7 @@
         <v>45986</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60226,7 +60226,7 @@
         <v>46003</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>44092</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>44013</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60450,7 +60450,7 @@
         <v>44684</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60523,7 +60523,7 @@
         <v>44735</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>45223</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60679,7 +60679,7 @@
         <v>44949</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60752,7 +60752,7 @@
         <v>45029</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60825,7 +60825,7 @@
         <v>45714</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60903,7 +60903,7 @@
         <v>45517</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45939</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>46090</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61132,7 +61132,7 @@
         <v>46050</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45869</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45485</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>46244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45335</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>46043</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45954</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>46009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>45335</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>44937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>46075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45328</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45070</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45226</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44817</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45964</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>46166</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44879</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45335</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45027</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>45370</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44904</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45335</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44911</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>45982</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>46055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>44755</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>46104</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>46050</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44792</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44893</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>46030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45547</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45978</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45978</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44873</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44488</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44718</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>45677</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45424</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45440</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45919</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>46145</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45954</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>46155</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>45352</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44593</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46013</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44960</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>46045</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45435</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45435</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45390</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46078</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45677</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45530</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45103</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45056</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>46232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45603</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>46240</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45145</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>46295</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45624</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45820</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45702</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44260</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>46268</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44560</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44870</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44811</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44505</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44656</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44522</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>44494</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44510</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44648</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44767</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44733</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44774</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44753</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44873</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44652</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44659</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44812</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44648</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44732</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44581</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44790</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44873</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44623</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44705</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44690</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>44510</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44613</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44659</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44491</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44676</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44812</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44502</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44530</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44505</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44505</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44614</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44767</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44662</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>44825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>44887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44747</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>44784</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>44783</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44733</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>44733</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44804</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44733</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>44613</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>44614</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44830</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>44536</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>44679</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>44853</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44701</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44704</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>44578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44722</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>44539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>44658</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>44652</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>44522</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>44882</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44862</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>44531</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44530</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44537</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>44748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44719</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>44813</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>44525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44709</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44709</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>44537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44729</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44505</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44627</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45365</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>44774</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45268</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45370</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>44865</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45424</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44515</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45301</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45443</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44509</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45110</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45210</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45210</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>44529</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>44579</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45143</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45378</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44620</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44582</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45352</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>44837</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44846</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44992</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45201</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45258</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>44957</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44839</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45672</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45419</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45037</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45419</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45044</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45424</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45443</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44733</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45166</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45148</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44977</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44990</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44964</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45244</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45393</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44844</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45146</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44968</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45159</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44529</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45271</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44525</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>44543</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45540</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>44825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45545</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44859</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45161</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>44623</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44879</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45335</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45729</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44649</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44744</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45315</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45145</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45218</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45603</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45166</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45163</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45033</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45160</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45229</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44970</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44830</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45161</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45132</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45216</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44980</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>44976</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45043</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44867</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45329</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45359</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45258</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44510</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45008</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45183</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45082</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44579</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44678</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44812</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45733</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45705</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45379</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44810</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>44620</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>45001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45730</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45278</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44811</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44810</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>44774</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>44817</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44830</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45729</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45729</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45518</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>44890</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45986</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44838</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44840</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44711</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45819</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>44965</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45826</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45365</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46139</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44967</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44529</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45559</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45819</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45888</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44690</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44865</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45702</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45854</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44960</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45524</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45706</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45930</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>44853</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45685</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44880</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45166</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>46058</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45356</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45096</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44536</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44767</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45187</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44676</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45370</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>44784</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>44553</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45915</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>46145</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44938</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44881</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44825</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44988</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45919</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>46145</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45058</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45216</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44607</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44964</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44995</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>46149</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>46149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44964</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45170</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>44634</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45076</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45855</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45855</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45855</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45072</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44858</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45350</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45729</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45938</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45944</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45946</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45027</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45761</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45343</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>44943</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44943</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45900</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44650</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>46155</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44740</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45364</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45351</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45820</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45410</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45954</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45954</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45106</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45798</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45940</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>44537</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>44938</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44783</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>44977</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44837</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45352</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44998</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>44837</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>44837</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>44988</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45202</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45729</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>45721</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45224</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45224</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45970</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45162</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45349</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>46084</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>46072</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>46084</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45978</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44525</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45384</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>44957</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>46163</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45978</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>44578</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45743</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>45979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45112</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44936</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45603</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45980</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45982</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44936</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45721</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45721</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45604</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45329</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>46168</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45993</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45993</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46086</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45993</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>45993</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45414</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46120</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45993</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>46169</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44616</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>44645</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>45999</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45999</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45630</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>46001</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45603</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44727</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>44549</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46007</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45029</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46006</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46006</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46009</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45061</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45061</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44579</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45461</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44517</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>46010</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45343</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46010</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46010</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45149</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45373</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45418</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45603</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>44579</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45398</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45143</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>46027</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45985</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>46176</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>44916</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>45166</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>46030</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46176</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>46176</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>46034</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>44582</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46036</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46036</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46036</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>46036</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46042</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45348</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45327</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46041</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46041</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44812</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45279</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>44960</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45604</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>46049</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45630</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46049</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46049</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>46049</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>46050</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>46183</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>46182</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44783</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44858</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44942</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>45986</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>45056</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>46184</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45986</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>46184</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46184</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>46184</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44911</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45005</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>44530</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45986</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>44959</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45162</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46071</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44938</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45712</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>46071</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45085</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46071</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>44790</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45069</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>46185</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45474</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>45624</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44992</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45985</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44798</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44728</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45674</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44799</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44881</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45148</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>46093</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>46093</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45798</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44525</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>44525</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>44846</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46100</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45222</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>44960</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>44960</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>44575</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45546</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45019</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>45051</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>46195</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45146</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>45174</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>45307</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>44938</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>46198</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45924</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>46114</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>44938</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45330</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45075</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>44725</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>44606</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>44525</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45110</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45733</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>44575</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>44879</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>45096</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>44958</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>44946</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46135</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>45166</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45559</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>44494</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>45110</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45964</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45114</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45170</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44901</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45425</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45762</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>44711</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>46030</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>44649</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>44944</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45520</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>44497</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>44496</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>44774</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45564</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45452</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>46211</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45685</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45685</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>46211</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45441</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>45537</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45667</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>44784</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45098</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45756</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>46222</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>45044</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>45044</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45385</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45062</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45289</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>46125</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>44536</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>45107</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>46228</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>44869</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>44546</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50801,7 +50801,7 @@
         <v>44893</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>45350</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>44976</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51025,7 +51025,7 @@
         <v>45602</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>44585</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45098</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>46234</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>44960</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45370</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>44757</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45181</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45329</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45218</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>46237</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45603</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>46280</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45350</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>46239</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>44949</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>45243</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>46283</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>44784</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44546</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>46240</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>44812</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>46283</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>46244</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>44575</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45132</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>44579</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45224</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45062</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>46287</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45306</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>44910</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>46245</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53494,7 +53494,7 @@
         <v>44869</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45261</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>44938</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45398</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>44575</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45628</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53947,7 +53947,7 @@
         <v>45062</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54020,7 +54020,7 @@
         <v>45310</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>44652</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54171,7 +54171,7 @@
         <v>46245</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54249,7 +54249,7 @@
         <v>44950</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>44977</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>46245</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>46293</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>44932</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>44932</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>46247</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54775,7 +54775,7 @@
         <v>46030</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45173</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45945</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55004,7 +55004,7 @@
         <v>44880</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>45040</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>44725</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>44784</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>46290</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>46293</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>45029</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>46293</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>44858</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>44968</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45160</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45160</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45686</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>45727</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45365</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>45306</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45288</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>46252</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45547</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>44995</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>44581</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45148</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45712</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>44725</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>44966</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>44540</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>46253</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>46100</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>46253</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45034</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>44830</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>45153</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>44489</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>45775</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57775,7 +57775,7 @@
         <v>45190</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57853,7 +57853,7 @@
         <v>44968</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45635</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57999,7 +57999,7 @@
         <v>45524</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>45637</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58145,7 +58145,7 @@
         <v>46307</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>46003</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45611</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58369,7 +58369,7 @@
         <v>46307</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58447,7 +58447,7 @@
         <v>46307</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>45239</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45672</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>45733</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45817</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>45817</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>45817</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>45819</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>45743</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>45986</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59202,7 +59202,7 @@
         <v>45831</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45831</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>45834</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45834</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59499,7 +59499,7 @@
         <v>45834</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>45834</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>45841</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59718,7 +59718,7 @@
         <v>45842</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>45842</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>45842</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45844</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45842</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60083,7 +60083,7 @@
         <v>45737</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60156,7 +60156,7 @@
         <v>45860</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>44944</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60307,7 +60307,7 @@
         <v>44092</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44013</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>45223</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>44684</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>44949</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60682,7 +60682,7 @@
         <v>44735</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45029</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>45714</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45517</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45939</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61067,7 +61067,7 @@
         <v>46090</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>46050</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>44729</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45869</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45485</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>46244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45335</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>46043</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44746</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45954</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>46009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45518</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>45335</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>44937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>46075</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>45328</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>45070</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>45226</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44817</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45964</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>46166</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>44879</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>45335</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45027</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>45210</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>45370</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44904</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45335</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44911</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>45982</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>46055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>44755</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>46104</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>46050</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44792</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46286</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44893</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>46030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45547</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45978</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45978</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44825</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44873</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44488</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44718</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>45677</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45424</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45440</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45919</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>46145</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45943</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45252</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45954</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>46155</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>45352</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>45993</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44593</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46013</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44960</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>46045</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45435</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45435</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>45390</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46078</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45677</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45530</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>45103</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45056</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>46217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>46232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45385</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45603</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>46240</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45145</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>46295</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45624</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45820</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45702</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44260</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>46268</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44560</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44870</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44811</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44505</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44656</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44522</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>44494</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44510</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>44648</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44767</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>44775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44733</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44774</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44753</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44873</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>44652</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>44659</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44812</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44648</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>44732</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>44581</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44790</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>44873</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44623</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44705</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44690</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>44510</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44613</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44659</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44491</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>44676</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>44812</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44502</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44530</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44505</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44505</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44614</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44767</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44662</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>44825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>44887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44747</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>44784</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>44783</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44733</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>44733</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44804</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44733</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>44613</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>44614</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>44830</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>44536</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>44679</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>44853</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44701</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44704</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>44578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44722</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>44539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>44658</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>44652</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>44522</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>44882</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>44862</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>44531</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44530</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>44537</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>44748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44719</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>44813</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>44525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>44709</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>44709</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>44537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>44729</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44505</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44627</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45365</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>44774</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45268</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>45370</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>44865</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45424</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44515</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45301</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45443</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>44509</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45110</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45210</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45210</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>44529</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>44579</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45143</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45378</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>44620</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44582</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45352</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>44837</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>44846</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44992</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45201</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45258</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>44957</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44839</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45672</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45419</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45037</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45419</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45044</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45424</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45443</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44733</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45166</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45148</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44977</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44990</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44964</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45244</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45393</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44844</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45146</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44968</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45159</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44529</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45271</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44525</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>44543</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45540</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>44825</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45545</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44859</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>45161</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>44623</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23135,7 +23135,7 @@
         <v>44879</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45335</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45729</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44649</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>44744</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45315</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45145</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45218</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45603</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45166</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45163</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45033</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45160</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45229</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>44970</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>44830</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45161</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45132</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>45216</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44980</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>44976</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45043</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44867</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45162</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45329</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45359</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45258</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44510</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45008</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45183</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45082</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44579</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44678</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44812</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45733</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45705</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45379</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44810</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>44620</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>45001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45730</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45278</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>44811</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44810</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>44774</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>44817</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44830</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45729</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45729</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45518</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>44890</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45986</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44838</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44840</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44711</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45819</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>44965</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45826</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45365</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46139</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44967</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44529</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45559</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45819</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45888</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44690</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44865</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45702</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45854</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44960</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45524</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45706</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45930</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>44853</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45685</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44880</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45166</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>46058</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45356</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45096</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44536</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44767</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45187</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44676</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45370</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>44784</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>44553</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45915</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29923,7 +29923,7 @@
         <v>46145</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44938</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
         <v>44881</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>44825</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44988</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45919</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>46145</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45058</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45216</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44607</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44964</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44995</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>46149</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>46149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44964</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         <v>45170</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>44634</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45076</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45855</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>45855</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45855</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>45072</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44858</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45350</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45729</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45938</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45944</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45946</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45027</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45761</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45343</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>44943</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44943</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45900</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44650</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>46155</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44740</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45364</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45351</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45820</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45410</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45954</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45954</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45106</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45798</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45940</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>44537</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>44938</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44974</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44783</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>44977</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44837</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34018,7 +34018,7 @@
         <v>45352</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>44998</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>44837</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>44837</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>44988</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45202</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45729</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>45721</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45224</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34680,7 +34680,7 @@
         <v>45224</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45970</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45162</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45349</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>46084</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>46072</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>46084</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>45978</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44525</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45384</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>44957</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>46163</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45978</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>44578</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45743</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>45979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45112</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>44936</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45603</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>45980</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45982</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>44936</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45721</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45721</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45604</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45329</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>46168</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45993</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>45993</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46086</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45993</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>45993</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45414</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46120</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45993</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>46169</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44616</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>44645</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>45999</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45999</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45630</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>46001</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44698</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45603</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44727</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>44549</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46007</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45029</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46006</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46006</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46009</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45061</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45061</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>44579</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45461</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>44517</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>46010</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45343</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46010</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46010</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45149</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45373</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45418</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45603</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>44579</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45398</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45143</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>46027</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45985</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>46176</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>44916</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>45166</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>46030</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46176</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>46176</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>46034</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>44582</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>46036</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46036</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46036</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>46036</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46042</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45348</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45327</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46041</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46041</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>44812</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45279</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>44960</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45604</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>46049</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45630</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46049</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46049</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>46049</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>46050</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>46183</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>46182</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44783</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44858</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44942</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>45986</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>45056</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>46184</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45986</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>46184</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46184</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>46184</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44911</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45005</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>44530</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45986</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>44959</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45162</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46071</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44938</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45712</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>46071</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45085</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46071</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>44790</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45069</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44038,7 +44038,7 @@
         <v>46185</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44111,7 +44111,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44184,7 +44184,7 @@
         <v>45474</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>45624</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44992</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45985</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44798</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44728</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45674</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44799</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44881</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45148</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>46093</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>46093</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45798</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44525</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>44525</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>44846</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46100</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45222</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>44960</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>44960</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>44575</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45546</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45019</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45878,7 +45878,7 @@
         <v>45051</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>46195</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45146</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>45174</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>45307</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>44938</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>46198</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45924</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>46114</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>44938</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46628,7 +46628,7 @@
         <v>45330</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45075</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>44725</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>44606</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>44525</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45110</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45733</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>44575</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>44879</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>45096</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>44958</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>44946</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46135</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>45166</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45559</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>44494</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>45110</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45964</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45114</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45170</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44901</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45425</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45762</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>44711</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>46030</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>44649</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>44944</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45520</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>44497</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>44496</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>44774</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45564</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45452</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>46211</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45685</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45685</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>46211</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45441</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>45537</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>45667</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>44784</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45098</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45756</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>46222</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>45044</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>45044</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45385</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45062</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45289</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>46125</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>44536</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>45107</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>46228</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>44869</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>44546</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50801,7 +50801,7 @@
         <v>44893</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>45350</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>44976</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51025,7 +51025,7 @@
         <v>45602</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>44585</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45098</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>46234</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>44960</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45370</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>44757</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45181</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45329</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45218</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>46237</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45603</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>46280</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45350</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>46239</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>44949</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>45243</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>46283</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>44784</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44546</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>46240</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>44812</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>46283</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>46244</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>44575</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45132</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52978,7 +52978,7 @@
         <v>44579</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45224</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>45062</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>46287</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45306</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>44910</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>46245</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53494,7 +53494,7 @@
         <v>44869</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45261</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>44938</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45398</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>44575</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45628</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53947,7 +53947,7 @@
         <v>45062</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54020,7 +54020,7 @@
         <v>45310</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54098,7 +54098,7 @@
         <v>44652</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54171,7 +54171,7 @@
         <v>46245</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54249,7 +54249,7 @@
         <v>44950</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>44977</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>46245</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>46293</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>44932</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>44932</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>46247</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54775,7 +54775,7 @@
         <v>46030</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45173</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45945</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55004,7 +55004,7 @@
         <v>44880</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>45040</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55155,7 +55155,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>44725</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55379,7 +55379,7 @@
         <v>44784</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>46290</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>46293</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>45029</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45288</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>46293</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>44858</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>44968</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>45160</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45160</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45686</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>45727</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45365</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>45306</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45288</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>46252</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45547</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56650,7 +56650,7 @@
         <v>44995</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>44581</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45148</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45712</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>44725</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>44966</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>44540</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>46253</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>46100</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>46253</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45034</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>44830</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>45153</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>44489</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>45775</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57775,7 +57775,7 @@
         <v>45190</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57853,7 +57853,7 @@
         <v>44968</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45635</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57999,7 +57999,7 @@
         <v>45524</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>45637</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58145,7 +58145,7 @@
         <v>46307</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>46003</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45611</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58369,7 +58369,7 @@
         <v>46307</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58447,7 +58447,7 @@
         <v>46307</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>45239</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>45672</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>45733</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
         <v>45817</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>45817</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>45817</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>45819</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>45743</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59129,7 +59129,7 @@
         <v>45986</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59202,7 +59202,7 @@
         <v>45831</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>45831</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>45834</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>45834</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59499,7 +59499,7 @@
         <v>45834</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>45834</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>45841</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59718,7 +59718,7 @@
         <v>45842</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>45842</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>45842</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45844</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45842</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60083,7 +60083,7 @@
         <v>45737</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60156,7 +60156,7 @@
         <v>45860</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>44944</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60307,7 +60307,7 @@
         <v>44092</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44013</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>45223</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>44684</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>44949</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60682,7 +60682,7 @@
         <v>44735</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45029</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>45714</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45517</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45939</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61067,7 +61067,7 @@
         <v>46090</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>46050</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>

--- a/Översikt NYKÖPING.xlsx
+++ b/Översikt NYKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45943</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45540</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>45952</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>45275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>44543</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>44760</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>45981</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44729</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45624</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>46244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>46290</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45978</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45485</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>46043</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44746</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45954</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>46075</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45518</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45335</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44531</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>45981</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>45070</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>45226</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>46166</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45964</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44817</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44631</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44812</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>44879</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45328</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>45335</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>45370</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>44893</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45982</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>46050</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>46286</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         <v>46030</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>46055</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45978</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45978</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>46104</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44904</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>45210</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44755</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45335</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>44792</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45027</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44911</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44825</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>44873</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44525</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>44718</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44593</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45919</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>45390</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45677</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>45424</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>45943</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>45385</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45435</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45056</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45954</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45252</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44935</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45603</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45993</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>46217</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>46232</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>46013</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>46280</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45624</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>46240</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>46045</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45820</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>46078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>46295</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45702</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45352</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45440</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>46145</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>46155</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45145</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45530</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44960</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45103</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45435</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>45210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45677</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44621</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44260</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46268</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>44560</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44870</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>44811</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44505</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44656</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44522</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44494</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44510</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44775</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44648</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44767</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44774</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44733</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44753</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44873</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44652</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44659</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44812</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44648</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>44732</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44581</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>44790</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44873</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44623</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44705</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44690</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>44510</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44659</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>44613</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>44530</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44676</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44812</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44502</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>44530</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>44498</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>44505</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44505</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44614</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>44767</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44662</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44825</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44747</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44784</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44783</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44733</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44733</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44804</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44733</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>44613</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44614</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44812</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44830</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>44536</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44679</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>44701</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>44853</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>44578</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44704</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44722</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>44539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>44658</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44652</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>44522</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44882</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44862</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>44531</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44530</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>44537</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>44748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44813</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>44719</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44709</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>44709</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>44537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>44729</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>44713</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45075</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44549</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>44977</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>44627</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>44869</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45702</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44505</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>44690</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>45008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>45166</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>44957</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45244</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>44784</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44783</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45062</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45370</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>44865</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45854</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>45604</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45330</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44946</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45343</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45685</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>45424</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44959</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44881</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45378</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>44858</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>44865</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45978</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45216</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45978</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>46084</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>46084</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44546</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>44968</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>44960</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>46072</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44964</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45166</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45474</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>46163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>44543</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>44830</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44867</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>44616</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45919</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45096</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>45098</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45098</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45029</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44525</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>44869</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>46086</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>46168</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45365</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>46120</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44976</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44964</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>46169</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45721</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>44825</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>44510</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45855</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45855</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45160</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45160</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>44837</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45564</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45855</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45855</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45729</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45441</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>44977</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44509</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45247</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45061</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45944</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45938</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>46098</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45398</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>44579</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44579</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>46176</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>46176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45370</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44582</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>44846</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45946</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45224</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45224</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>45145</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44817</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44579</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44517</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45365</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44837</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45163</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44578</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44859</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45520</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45062</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>44844</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>45143</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45900</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44725</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>46184</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>46184</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45954</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>45398</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>45667</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45954</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46183</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>46184</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45410</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>45258</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45820</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>46182</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>46185</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>46185</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>46185</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45798</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>46184</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45630</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>45310</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44774</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44968</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45043</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28379,7 +28379,7 @@
         <v>44880</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45364</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44881</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>46195</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>45762</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45970</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45148</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45798</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>44784</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45974</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45062</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45721</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>46198</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>44932</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44932</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>44942</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45359</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45174</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44774</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>44830</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45980</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45979</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44812</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44965</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45982</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45540</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45729</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45729</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>45268</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45288</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44529</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45384</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>46211</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45106</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45306</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45603</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>46211</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45993</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45993</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>45993</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45993</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>45993</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45443</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>45993</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>45424</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>44950</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45350</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45315</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45999</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>46222</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>45999</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45190</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>46001</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44968</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45775</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46228</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>46006</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46006</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46125</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>46007</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>44837</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>46237</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46010</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>46010</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>46010</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44949</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45635</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>46234</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45524</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>46027</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45637</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>46030</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>46239</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>46240</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>46034</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>46036</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>46283</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>46283</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>46036</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45611</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>46036</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>46036</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>46042</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>46041</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>46287</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>46041</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>46245</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>46244</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>46245</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>46245</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>46050</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45239</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>46049</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>46030</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>45518</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46247</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>46049</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>46049</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>46049</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>45672</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>46247</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45733</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>46293</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>46293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>45986</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36370,7 +36370,7 @@
         <v>45986</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45945</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45817</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>46293</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45986</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45817</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>46293</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45817</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45819</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>46071</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>46071</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37208,7 +37208,7 @@
         <v>46071</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45743</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>46252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>45985</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>46253</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45831</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45831</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45834</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45834</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>46253</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>45834</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>45834</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>46093</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>46093</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>44938</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>46100</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38391,7 +38391,7 @@
         <v>45842</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45842</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45841</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45842</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45603</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45842</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45603</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45161</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45844</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46100</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>44494</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>44936</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>45737</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44529</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>44536</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45860</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>44944</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45924</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>46114</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45373</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>44992</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>44978</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>44497</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45329</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>44525</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>46307</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45537</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45352</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45352</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>44890</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40626,7 +40626,7 @@
         <v>44529</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>46003</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>45393</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>46307</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45986</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>46307</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45819</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>45044</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>44525</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44525</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>45056</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45559</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>46135</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>45964</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>45559</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45930</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45819</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45826</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45706</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>46139</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45604</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45005</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45425</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45986</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44711</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>44938</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45110</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44620</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45370</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45546</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44896</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45261</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>46030</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45985</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>44537</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>44957</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>44911</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45051</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44944</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>46317</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>46058</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>44936</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>46145</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>46145</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>46317</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>44784</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45218</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45072</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>44992</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46149</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46149</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>45603</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45547</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>44990</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>46155</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45712</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>45940</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>44784</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45351</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45343</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>45027</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>44744</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>44966</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44893</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45110</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>45365</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>44812</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45258</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45624</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45763,7 +45763,7 @@
         <v>44958</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>44960</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>44964</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>44965</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45037</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>44965</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>44988</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45414</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45143</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45112</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>44998</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>44678</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45033</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45385</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45602</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45062</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45443</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>44733</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45210</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>44727</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45727</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>44740</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         <v>44977</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>44676</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45085</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>44582</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45216</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>45545</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>44858</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>44757</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45224</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45729</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>44575</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45729</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45210</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45761</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45110</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>45202</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45672</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45183</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45069</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>44910</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45733</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>44825</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>44943</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>44943</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45076</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45229</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45686</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45058</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45733</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>45170</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45162</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>44901</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45356</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45307</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45107</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45379</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>44960</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>45756</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50213,7 +50213,7 @@
         <v>45082</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45040</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>45350</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>44530</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45132</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>44496</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>44623</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45098</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>44579</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>45335</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>45279</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>45419</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51099,7 +51099,7 @@
         <v>45419</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51172,7 +51172,7 @@
         <v>45159</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>44553</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>44980</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>44995</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>44976</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45201</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45029</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>44579</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51766,7 +51766,7 @@
         <v>44525</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51844,7 +51844,7 @@
         <v>45418</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>44938</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>44575</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45148</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>44546</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45096</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45630</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45306</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         <v>45452</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52516,7 +52516,7 @@
         <v>45149</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45173</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>44536</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>45132</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45148</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52896,7 +52896,7 @@
         <v>45162</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45162</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>45243</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>44575</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53203,7 +53203,7 @@
         <v>45181</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>44581</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45146</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53427,7 +53427,7 @@
         <v>45160</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>44995</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>44515</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>45721</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>45329</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45329</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>44585</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>45114</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>44649</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45170</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45603</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>44606</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>44988</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45218</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>44839</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>44840</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45166</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54688,7 +54688,7 @@
         <v>45350</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54761,7 +54761,7 @@
         <v>45153</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54839,7 +54839,7 @@
         <v>44652</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45044</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54985,7 +54985,7 @@
         <v>45044</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45730</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         <v>44634</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>45061</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55282,7 +55282,7 @@
         <v>45187</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45674</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55428,7 +55428,7 @@
         <v>45161</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55501,7 +55501,7 @@
         <v>45146</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>45166</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>44711</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>44649</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>44811</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>44810</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>44838</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>44839</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>44728</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>45166</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>45685</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56319,7 +56319,7 @@
         <v>45685</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56397,7 +56397,7 @@
         <v>44725</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56470,7 +56470,7 @@
         <v>44774</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>44853</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56616,7 +56616,7 @@
         <v>45162</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>44645</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>44858</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>45222</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>45461</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>44799</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45705</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45712</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>44725</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45289</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>44798</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>44767</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>44846</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45348</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>45349</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57726,7 +57726,7 @@
         <v>44607</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>44810</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57872,7 +57872,7 @@
         <v>44974</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45092</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>44575</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58096,7 +58096,7 @@
         <v>45271</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58169,7 +58169,7 @@
         <v>45743</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58242,7 +58242,7 @@
         <v>44783</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>45278</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>44620</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58461,7 +58461,7 @@
         <v>45301</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>45628</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>44698</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>44540</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>44967</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>44830</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58909,7 +58909,7 @@
         <v>45524</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58982,7 +58982,7 @@
         <v>45327</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>44960</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59133,7 +59133,7 @@
         <v>44970</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59211,7 +59211,7 @@
         <v>44790</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>44880</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>44650</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>44837</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>44879</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>44879</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45001</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>44938</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59815,7 +59815,7 @@
         <v>44916</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59893,7 +59893,7 @@
         <v>45019</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59966,7 +59966,7 @@
         <v>44812</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60039,7 +60039,7 @@
         <v>44960</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>44938</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>44092</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>44013</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>44684</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60414,7 +60414,7 @@
         <v>44735</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45223</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60570,7 +60570,7 @@
         <v>44949</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45029</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45714</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45517</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>45939</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60950,7 +60950,7 @@
         <v>46090</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>46050</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
